--- a/data/datos_tp.xlsx
+++ b/data/datos_tp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\GitHub\analisis-demografico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://indecok-my.sharepoint.com/personal/agomezvargas_indec_gob_ar/Documents/Documentos/GitHub/analisis-demografico/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9476FF75-4DF4-4BBA-98C7-31E2FE37B715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{9476FF75-4DF4-4BBA-98C7-31E2FE37B715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D15910D-E6BE-4C10-9B0A-1AE811C8A709}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{AF598439-62DC-4F7D-BE55-398D701C39E6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="16" xr2:uid="{AF598439-62DC-4F7D-BE55-398D701C39E6}"/>
   </bookViews>
   <sheets>
     <sheet name="piramide" sheetId="9" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="211">
   <si>
     <t>semestre</t>
   </si>
@@ -675,6 +675,18 @@
   </si>
   <si>
     <t>15-64 años</t>
+  </si>
+  <si>
+    <t>envejecimiento</t>
+  </si>
+  <si>
+    <t>sobreenvejecimiento_t</t>
+  </si>
+  <si>
+    <t>sobreenvejecimiento_m</t>
+  </si>
+  <si>
+    <t>sobreenvejecimiento_v</t>
   </si>
 </sst>
 </file>
@@ -690,7 +702,7 @@
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="#,##0_ ;\-#,##0\ "/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -919,8 +931,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1058,6 +1076,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1442,7 +1478,7 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
@@ -1626,6 +1662,11 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="136">
     <cellStyle name="20% - Accent1 2" xfId="58" xr:uid="{4D1EAED0-96CA-441D-9C13-E5B4EEB66841}"/>
@@ -3257,8 +3298,12 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D1CF82-49B4-4F76-B978-57349D795049}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="10" max="10" width="11.5546875" style="71"/>
+    <col min="11" max="13" width="11.5546875" style="24"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" t="s">
@@ -3299,146 +3344,129 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2">
-        <v>2018</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B2" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="C2">
-        <v>3018200</v>
-      </c>
-      <c r="D2">
-        <v>951227</v>
-      </c>
-      <c r="E2">
-        <v>2251437</v>
-      </c>
-      <c r="F2">
-        <v>204809</v>
-      </c>
-      <c r="G2">
-        <v>31.5</v>
-      </c>
-      <c r="H2">
-        <v>74.599999999999994</v>
-      </c>
-      <c r="I2">
-        <v>6.8</v>
-      </c>
-      <c r="K2" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="24" t="s">
+      <c r="C2" s="73">
+        <v>3053223</v>
+      </c>
+      <c r="D2" s="73">
+        <v>985536</v>
+      </c>
+      <c r="E2" s="73">
+        <v>2269234</v>
+      </c>
+      <c r="F2" s="73">
+        <v>191215</v>
+      </c>
+      <c r="G2" s="73">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="H2" s="73">
+        <v>74.3</v>
+      </c>
+      <c r="I2" s="73">
+        <v>6.3</v>
+      </c>
+      <c r="J2" s="75"/>
+      <c r="M2" s="74" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3">
-        <v>2018</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B3" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="C3">
-        <v>4041006</v>
-      </c>
-      <c r="D3">
-        <v>593218</v>
-      </c>
-      <c r="E3">
-        <v>3649248</v>
-      </c>
-      <c r="F3">
-        <v>266075</v>
-      </c>
-      <c r="G3">
-        <v>14.7</v>
-      </c>
-      <c r="H3">
-        <v>90.3</v>
-      </c>
-      <c r="I3">
-        <v>6.6</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="L3" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="24" t="s">
+      <c r="C3" s="73">
+        <v>4018256</v>
+      </c>
+      <c r="D3" s="73">
+        <v>528950</v>
+      </c>
+      <c r="E3" s="73">
+        <v>3580958</v>
+      </c>
+      <c r="F3" s="73">
+        <v>214885</v>
+      </c>
+      <c r="G3" s="73">
+        <v>13.2</v>
+      </c>
+      <c r="H3" s="73">
+        <v>89.1</v>
+      </c>
+      <c r="I3" s="73">
+        <v>5.3</v>
+      </c>
+      <c r="J3" s="75"/>
+      <c r="M3" s="74" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4">
-        <v>2018</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B4" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C4">
-        <v>7059206</v>
-      </c>
-      <c r="D4">
-        <v>1544445</v>
-      </c>
-      <c r="E4">
-        <v>5900685</v>
-      </c>
-      <c r="F4">
-        <v>470884</v>
-      </c>
-      <c r="G4">
-        <v>21.9</v>
-      </c>
-      <c r="H4">
-        <v>83.6</v>
-      </c>
-      <c r="I4">
-        <v>6.7</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="24" t="s">
-        <v>31</v>
-      </c>
+      <c r="C4" s="73">
+        <v>7071479</v>
+      </c>
+      <c r="D4" s="73">
+        <v>1514486</v>
+      </c>
+      <c r="E4" s="73">
+        <v>5850192</v>
+      </c>
+      <c r="F4" s="73">
+        <v>406100</v>
+      </c>
+      <c r="G4" s="73">
+        <v>21.4</v>
+      </c>
+      <c r="H4" s="73">
+        <v>82.7</v>
+      </c>
+      <c r="I4" s="73">
+        <v>5.7</v>
+      </c>
+      <c r="J4" s="75"/>
+      <c r="M4" s="74"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
       </c>
       <c r="C5">
-        <v>3076390</v>
+        <v>3018200</v>
       </c>
       <c r="D5">
-        <v>1005257</v>
+        <v>951227</v>
       </c>
       <c r="E5">
-        <v>2263218</v>
+        <v>2251437</v>
       </c>
       <c r="F5">
-        <v>218227</v>
+        <v>204809</v>
       </c>
       <c r="G5">
-        <v>32.700000000000003</v>
+        <v>31.5</v>
       </c>
       <c r="H5">
-        <v>73.599999999999994</v>
+        <v>74.599999999999994</v>
       </c>
       <c r="I5">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="K5" s="24" t="s">
         <v>31</v>
@@ -3452,31 +3480,31 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B6" t="s">
         <v>33</v>
       </c>
       <c r="C6">
-        <v>4027390</v>
+        <v>4041006</v>
       </c>
       <c r="D6">
-        <v>561000</v>
+        <v>593218</v>
       </c>
       <c r="E6">
-        <v>3558004</v>
+        <v>3649248</v>
       </c>
       <c r="F6">
-        <v>283034</v>
+        <v>266075</v>
       </c>
       <c r="G6">
-        <v>13.9</v>
+        <v>14.7</v>
       </c>
       <c r="H6">
-        <v>88.3</v>
+        <v>90.3</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="K6" s="24" t="s">
         <v>31</v>
@@ -3490,31 +3518,31 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B7" t="s">
         <v>10</v>
       </c>
       <c r="C7">
-        <v>7103780</v>
+        <v>7059206</v>
       </c>
       <c r="D7">
-        <v>1566257</v>
+        <v>1544445</v>
       </c>
       <c r="E7">
-        <v>5821222</v>
+        <v>5900685</v>
       </c>
       <c r="F7">
-        <v>501261</v>
+        <v>470884</v>
       </c>
       <c r="G7">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="H7">
-        <v>81.900000000000006</v>
+        <v>83.6</v>
       </c>
       <c r="I7">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="K7" s="24" t="s">
         <v>31</v>
@@ -3528,31 +3556,31 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8">
-        <v>2621381</v>
+        <v>3076390</v>
       </c>
       <c r="D8">
-        <v>756501</v>
+        <v>1005257</v>
       </c>
       <c r="E8">
-        <v>1913535</v>
+        <v>2263218</v>
       </c>
       <c r="F8">
-        <v>230599</v>
+        <v>218227</v>
       </c>
       <c r="G8">
-        <v>28.9</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="H8">
-        <v>73</v>
+        <v>73.599999999999994</v>
       </c>
       <c r="I8">
-        <v>8.8000000000000007</v>
+        <v>7.1</v>
       </c>
       <c r="K8" s="24" t="s">
         <v>31</v>
@@ -3566,31 +3594,31 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
       <c r="C9">
-        <v>3409171</v>
+        <v>4027390</v>
       </c>
       <c r="D9">
-        <v>377347</v>
+        <v>561000</v>
       </c>
       <c r="E9">
-        <v>2998343</v>
+        <v>3558004</v>
       </c>
       <c r="F9">
-        <v>282573</v>
+        <v>283034</v>
       </c>
       <c r="G9">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="H9">
-        <v>87.9</v>
+        <v>88.3</v>
       </c>
       <c r="I9">
-        <v>8.3000000000000007</v>
+        <v>7</v>
       </c>
       <c r="K9" s="24" t="s">
         <v>31</v>
@@ -3604,31 +3632,31 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
-        <v>6030552</v>
+        <v>7103780</v>
       </c>
       <c r="D10">
-        <v>1133848</v>
+        <v>1566257</v>
       </c>
       <c r="E10">
-        <v>4911878</v>
+        <v>5821222</v>
       </c>
       <c r="F10">
-        <v>513172</v>
+        <v>501261</v>
       </c>
       <c r="G10">
-        <v>18.8</v>
+        <v>22</v>
       </c>
       <c r="H10">
-        <v>81.400000000000006</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="I10">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="K10" s="24" t="s">
         <v>31</v>
@@ -3642,31 +3670,31 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11">
-        <v>2898146</v>
+        <v>2621381</v>
       </c>
       <c r="D11">
-        <v>1047582</v>
+        <v>756501</v>
       </c>
       <c r="E11">
-        <v>1988282</v>
+        <v>1913535</v>
       </c>
       <c r="F11">
-        <v>201825</v>
+        <v>230599</v>
       </c>
       <c r="G11">
-        <v>36.1</v>
+        <v>28.9</v>
       </c>
       <c r="H11">
-        <v>68.599999999999994</v>
+        <v>73</v>
       </c>
       <c r="I11">
-        <v>7</v>
+        <v>8.8000000000000007</v>
       </c>
       <c r="K11" s="24" t="s">
         <v>31</v>
@@ -3680,31 +3708,31 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12">
-        <v>3710307</v>
+        <v>3409171</v>
       </c>
       <c r="D12">
-        <v>488463</v>
+        <v>377347</v>
       </c>
       <c r="E12">
-        <v>3215819</v>
+        <v>2998343</v>
       </c>
       <c r="F12">
-        <v>220936</v>
+        <v>282573</v>
       </c>
       <c r="G12">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="H12">
-        <v>86.7</v>
+        <v>87.9</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="K12" s="24" t="s">
         <v>31</v>
@@ -3718,31 +3746,31 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B13" t="s">
         <v>10</v>
       </c>
       <c r="C13">
-        <v>6608453</v>
+        <v>6030552</v>
       </c>
       <c r="D13">
-        <v>1536045</v>
+        <v>1133848</v>
       </c>
       <c r="E13">
-        <v>5204101</v>
+        <v>4911878</v>
       </c>
       <c r="F13">
-        <v>422761</v>
+        <v>513172</v>
       </c>
       <c r="G13">
-        <v>23.2</v>
+        <v>18.8</v>
       </c>
       <c r="H13">
-        <v>78.7</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="I13">
-        <v>6.4</v>
+        <v>8.5</v>
       </c>
       <c r="K13" s="24" t="s">
         <v>31</v>
@@ -3756,31 +3784,31 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14">
-        <v>2909899</v>
+        <v>2898146</v>
       </c>
       <c r="D14">
-        <v>1027212</v>
+        <v>1047582</v>
       </c>
       <c r="E14">
-        <v>2109983</v>
+        <v>1988282</v>
       </c>
       <c r="F14">
-        <v>196205</v>
+        <v>201825</v>
       </c>
       <c r="G14">
-        <v>35.299999999999997</v>
+        <v>36.1</v>
       </c>
       <c r="H14">
-        <v>72.5</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="I14">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="K14" s="24" t="s">
         <v>31</v>
@@ -3794,31 +3822,31 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15">
-        <v>3845623</v>
+        <v>3710307</v>
       </c>
       <c r="D15">
-        <v>533916</v>
+        <v>488463</v>
       </c>
       <c r="E15">
-        <v>3389719</v>
+        <v>3215819</v>
       </c>
       <c r="F15">
-        <v>249676</v>
+        <v>220936</v>
       </c>
       <c r="G15">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="H15">
-        <v>88.1</v>
+        <v>86.7</v>
       </c>
       <c r="I15">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="24" t="s">
         <v>31</v>
@@ -3832,31 +3860,31 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B16" t="s">
         <v>10</v>
       </c>
       <c r="C16">
-        <v>6755522</v>
+        <v>6608453</v>
       </c>
       <c r="D16">
-        <v>1561128</v>
+        <v>1536045</v>
       </c>
       <c r="E16">
-        <v>5499702</v>
+        <v>5204101</v>
       </c>
       <c r="F16">
-        <v>445881</v>
+        <v>422761</v>
       </c>
       <c r="G16">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="H16">
-        <v>81.400000000000006</v>
+        <v>78.7</v>
       </c>
       <c r="I16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="K16" s="24" t="s">
         <v>31</v>
@@ -3870,31 +3898,31 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
       <c r="C17">
-        <v>2892418</v>
+        <v>2909899</v>
       </c>
       <c r="D17">
-        <v>1021051</v>
+        <v>1027212</v>
       </c>
       <c r="E17">
-        <v>2106085</v>
+        <v>2109983</v>
       </c>
       <c r="F17">
-        <v>180280</v>
+        <v>196205</v>
       </c>
       <c r="G17">
         <v>35.299999999999997</v>
       </c>
       <c r="H17">
-        <v>72.8</v>
+        <v>72.5</v>
       </c>
       <c r="I17">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="K17" s="24" t="s">
         <v>31</v>
@@ -3908,31 +3936,31 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18">
-        <v>3875911</v>
+        <v>3845623</v>
       </c>
       <c r="D18">
-        <v>577074</v>
+        <v>533916</v>
       </c>
       <c r="E18">
-        <v>3466663</v>
+        <v>3389719</v>
       </c>
       <c r="F18">
-        <v>267574</v>
+        <v>249676</v>
       </c>
       <c r="G18">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="H18">
-        <v>89.4</v>
+        <v>88.1</v>
       </c>
       <c r="I18">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="K18" s="24" t="s">
         <v>31</v>
@@ -3946,28 +3974,28 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
       </c>
       <c r="C19">
-        <v>6768329</v>
+        <v>6755522</v>
       </c>
       <c r="D19">
-        <v>1598125</v>
+        <v>1561128</v>
       </c>
       <c r="E19">
-        <v>5572748</v>
+        <v>5499702</v>
       </c>
       <c r="F19">
-        <v>447854</v>
+        <v>445881</v>
       </c>
       <c r="G19">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="H19">
-        <v>82.3</v>
+        <v>81.400000000000006</v>
       </c>
       <c r="I19">
         <v>6.6</v>
@@ -3979,6 +4007,120 @@
         <v>31</v>
       </c>
       <c r="M19" s="24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>2023</v>
+      </c>
+      <c r="B20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>2892418</v>
+      </c>
+      <c r="D20">
+        <v>1021051</v>
+      </c>
+      <c r="E20">
+        <v>2106085</v>
+      </c>
+      <c r="F20">
+        <v>180280</v>
+      </c>
+      <c r="G20">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="H20">
+        <v>72.8</v>
+      </c>
+      <c r="I20">
+        <v>6.2</v>
+      </c>
+      <c r="K20" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L20" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M20" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>2023</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21">
+        <v>3875911</v>
+      </c>
+      <c r="D21">
+        <v>577074</v>
+      </c>
+      <c r="E21">
+        <v>3466663</v>
+      </c>
+      <c r="F21">
+        <v>267574</v>
+      </c>
+      <c r="G21">
+        <v>14.9</v>
+      </c>
+      <c r="H21">
+        <v>89.4</v>
+      </c>
+      <c r="I21">
+        <v>6.9</v>
+      </c>
+      <c r="K21" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M21" s="24" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>2023</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>6768329</v>
+      </c>
+      <c r="D22">
+        <v>1598125</v>
+      </c>
+      <c r="E22">
+        <v>5572748</v>
+      </c>
+      <c r="F22">
+        <v>447854</v>
+      </c>
+      <c r="G22">
+        <v>23.6</v>
+      </c>
+      <c r="H22">
+        <v>82.3</v>
+      </c>
+      <c r="I22">
+        <v>6.6</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="L22" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="24" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4925,7 +5067,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B8C7B6-1F60-4FD3-99BE-80BE227B7C13}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -4947,67 +5089,67 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
       <c r="C2">
-        <v>68.400000000000006</v>
+        <v>68.599999999999994</v>
       </c>
       <c r="D2">
-        <v>63.1</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="E2">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
       </c>
       <c r="C3">
-        <v>47.4</v>
+        <v>45.2</v>
       </c>
       <c r="D3">
-        <v>42.5</v>
+        <v>41.3</v>
       </c>
       <c r="E3">
-        <v>10.4</v>
+        <v>8.8000000000000007</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
       </c>
       <c r="C4">
-        <v>69.099999999999994</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="D4">
-        <v>63.3</v>
+        <v>63.1</v>
       </c>
       <c r="E4">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
       <c r="C5">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
       <c r="D5">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="E5">
         <v>10.4</v>
@@ -5015,137 +5157,171 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
       <c r="C6">
-        <v>64.900000000000006</v>
+        <v>69.099999999999994</v>
       </c>
       <c r="D6">
-        <v>58.3</v>
+        <v>63.3</v>
       </c>
       <c r="E6">
-        <v>10.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B7" t="s">
         <v>33</v>
       </c>
       <c r="C7">
-        <v>44.9</v>
+        <v>47.6</v>
       </c>
       <c r="D7">
-        <v>39.1</v>
+        <v>42.7</v>
       </c>
       <c r="E7">
-        <v>12.9</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8">
-        <v>68.8</v>
+        <v>64.900000000000006</v>
       </c>
       <c r="D8">
-        <v>64</v>
+        <v>58.3</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>10.199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
       <c r="C9">
-        <v>48.6</v>
+        <v>44.9</v>
       </c>
       <c r="D9">
-        <v>44.2</v>
+        <v>39.1</v>
       </c>
       <c r="E9">
-        <v>9</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10">
-        <v>70.2</v>
+        <v>68.8</v>
       </c>
       <c r="D10">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11">
-        <v>49</v>
+        <v>48.6</v>
       </c>
       <c r="D11">
-        <v>45.3</v>
+        <v>44.2</v>
       </c>
       <c r="E11">
-        <v>7.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12">
-        <v>70.3</v>
+        <v>70.2</v>
       </c>
       <c r="D12">
-        <v>66.900000000000006</v>
+        <v>66</v>
       </c>
       <c r="E12">
-        <v>4.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B13" t="s">
         <v>33</v>
       </c>
       <c r="C13">
+        <v>49</v>
+      </c>
+      <c r="D13">
+        <v>45.3</v>
+      </c>
+      <c r="E13">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <v>2023</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>70.3</v>
+      </c>
+      <c r="D14">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="E14">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15">
         <v>51.1</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>48</v>
       </c>
-      <c r="E13">
+      <c r="E15">
         <v>6.1</v>
       </c>
     </row>
@@ -5156,7 +5332,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007A4407-574F-4237-9E16-A68B67AE9EBF}">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -5195,323 +5371,323 @@
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2">
-        <v>2018</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B2" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="D2">
-        <v>2216890</v>
-      </c>
-      <c r="E2">
-        <v>300013</v>
-      </c>
-      <c r="F2">
-        <v>666935</v>
-      </c>
-      <c r="G2">
-        <v>1249942</v>
-      </c>
-      <c r="H2">
+      <c r="D2" s="73">
+        <v>2262945</v>
+      </c>
+      <c r="E2" s="73">
+        <v>270582</v>
+      </c>
+      <c r="F2" s="73">
+        <v>723595</v>
+      </c>
+      <c r="G2" s="73">
+        <v>1268768</v>
+      </c>
+      <c r="H2" s="73">
         <v>0</v>
       </c>
-      <c r="I2">
-        <v>13.5</v>
-      </c>
-      <c r="J2">
-        <v>30.1</v>
-      </c>
-      <c r="K2">
-        <v>56.4</v>
+      <c r="I2" s="73">
+        <v>12</v>
+      </c>
+      <c r="J2" s="73">
+        <v>32</v>
+      </c>
+      <c r="K2" s="73">
+        <v>56.1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3">
-        <v>2018</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="A3" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B3" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="D3">
-        <v>2707923</v>
-      </c>
-      <c r="E3">
-        <v>545494</v>
-      </c>
-      <c r="F3">
-        <v>824714</v>
-      </c>
-      <c r="G3">
-        <v>1337715</v>
-      </c>
-      <c r="H3">
+      <c r="D3" s="73">
+        <v>2771973</v>
+      </c>
+      <c r="E3" s="73">
+        <v>550300</v>
+      </c>
+      <c r="F3" s="73">
+        <v>855776</v>
+      </c>
+      <c r="G3" s="73">
+        <v>1365897</v>
+      </c>
+      <c r="H3" s="73">
         <v>0</v>
       </c>
-      <c r="I3">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="J3">
-        <v>30.5</v>
-      </c>
-      <c r="K3">
-        <v>49.4</v>
+      <c r="I3" s="73">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="J3" s="73">
+        <v>30.9</v>
+      </c>
+      <c r="K3" s="73">
+        <v>49.3</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4">
-        <v>2018</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="A4" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B4" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="D4">
-        <v>820183</v>
-      </c>
-      <c r="E4">
-        <v>125502</v>
-      </c>
-      <c r="F4">
-        <v>386785</v>
-      </c>
-      <c r="G4">
-        <v>307896</v>
-      </c>
-      <c r="H4">
+      <c r="D4" s="73">
+        <v>841966</v>
+      </c>
+      <c r="E4" s="73">
+        <v>129884</v>
+      </c>
+      <c r="F4" s="73">
+        <v>412808</v>
+      </c>
+      <c r="G4" s="73">
+        <v>299274</v>
+      </c>
+      <c r="H4" s="73">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>15.3</v>
-      </c>
-      <c r="J4">
-        <v>47.2</v>
-      </c>
-      <c r="K4">
-        <v>37.5</v>
+      <c r="I4" s="73">
+        <v>15.4</v>
+      </c>
+      <c r="J4" s="73">
+        <v>49</v>
+      </c>
+      <c r="K4" s="73">
+        <v>35.5</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5">
-        <v>2018</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="A5" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B5" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="D5">
-        <v>1399618</v>
-      </c>
-      <c r="E5">
-        <v>505927</v>
-      </c>
-      <c r="F5">
-        <v>356460</v>
-      </c>
-      <c r="G5">
-        <v>537231</v>
-      </c>
-      <c r="H5">
+      <c r="D5" s="73">
+        <v>1332402</v>
+      </c>
+      <c r="E5" s="73">
+        <v>476323</v>
+      </c>
+      <c r="F5" s="73">
+        <v>365203</v>
+      </c>
+      <c r="G5" s="73">
+        <v>490876</v>
+      </c>
+      <c r="H5" s="73">
         <v>0</v>
       </c>
-      <c r="I5">
-        <v>36.1</v>
-      </c>
-      <c r="J5">
-        <v>25.5</v>
-      </c>
-      <c r="K5">
-        <v>38.4</v>
+      <c r="I5" s="73">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="J5" s="73">
+        <v>27.4</v>
+      </c>
+      <c r="K5" s="73">
+        <v>36.799999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6">
-        <v>2018</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="A6" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B6" s="73" t="s">
         <v>53</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D6">
-        <v>4924813</v>
-      </c>
-      <c r="E6">
-        <v>845507</v>
-      </c>
-      <c r="F6">
-        <v>1491649</v>
-      </c>
-      <c r="G6">
-        <v>2587657</v>
-      </c>
-      <c r="H6">
+      <c r="D6" s="73">
+        <v>5034918</v>
+      </c>
+      <c r="E6" s="73">
+        <v>820882</v>
+      </c>
+      <c r="F6" s="73">
+        <v>1579371</v>
+      </c>
+      <c r="G6" s="73">
+        <v>2634665</v>
+      </c>
+      <c r="H6" s="73">
         <v>0</v>
       </c>
-      <c r="I6">
-        <v>17.2</v>
-      </c>
-      <c r="J6">
-        <v>30.3</v>
-      </c>
-      <c r="K6">
-        <v>52.5</v>
+      <c r="I6" s="73">
+        <v>16.3</v>
+      </c>
+      <c r="J6" s="73">
+        <v>31.4</v>
+      </c>
+      <c r="K6" s="73">
+        <v>52.3</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7">
-        <v>2018</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="A7" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B7" s="73" t="s">
         <v>54</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D7">
-        <v>2219801</v>
-      </c>
-      <c r="E7">
-        <v>631429</v>
-      </c>
-      <c r="F7">
-        <v>743245</v>
-      </c>
-      <c r="G7">
-        <v>845127</v>
-      </c>
-      <c r="H7">
+      <c r="D7" s="73">
+        <v>2174368</v>
+      </c>
+      <c r="E7" s="73">
+        <v>606207</v>
+      </c>
+      <c r="F7" s="73">
+        <v>778011</v>
+      </c>
+      <c r="G7" s="73">
+        <v>790150</v>
+      </c>
+      <c r="H7" s="73">
         <v>0</v>
       </c>
-      <c r="I7">
-        <v>28.4</v>
-      </c>
-      <c r="J7">
-        <v>33.5</v>
-      </c>
-      <c r="K7">
-        <v>38.1</v>
+      <c r="I7" s="73">
+        <v>27.9</v>
+      </c>
+      <c r="J7" s="73">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="K7" s="73">
+        <v>36.299999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8">
-        <v>2018</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="A8" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B8" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="D8">
-        <v>3037073</v>
-      </c>
-      <c r="E8">
-        <v>425515</v>
-      </c>
-      <c r="F8">
-        <v>1053720</v>
-      </c>
-      <c r="G8">
-        <v>1557838</v>
-      </c>
-      <c r="H8">
+      <c r="D8" s="73">
+        <v>3104911</v>
+      </c>
+      <c r="E8" s="73">
+        <v>400466</v>
+      </c>
+      <c r="F8" s="73">
+        <v>1136403</v>
+      </c>
+      <c r="G8" s="73">
+        <v>1568042</v>
+      </c>
+      <c r="H8" s="73">
         <v>0</v>
       </c>
-      <c r="I8">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>34.700000000000003</v>
-      </c>
-      <c r="K8">
-        <v>51.3</v>
+      <c r="I8" s="73">
+        <v>12.9</v>
+      </c>
+      <c r="J8" s="73">
+        <v>36.6</v>
+      </c>
+      <c r="K8" s="73">
+        <v>50.5</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9">
-        <v>2018</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="A9" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B9" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="D9">
-        <v>4107541</v>
-      </c>
-      <c r="E9">
-        <v>1051421</v>
-      </c>
-      <c r="F9">
-        <v>1181174</v>
-      </c>
-      <c r="G9">
-        <v>1874946</v>
-      </c>
-      <c r="H9">
+      <c r="D9" s="73">
+        <v>4104375</v>
+      </c>
+      <c r="E9" s="73">
+        <v>1026623</v>
+      </c>
+      <c r="F9" s="73">
+        <v>1220979</v>
+      </c>
+      <c r="G9" s="73">
+        <v>1856773</v>
+      </c>
+      <c r="H9" s="73">
         <v>0</v>
       </c>
-      <c r="I9">
-        <v>25.6</v>
-      </c>
-      <c r="J9">
-        <v>28.8</v>
-      </c>
-      <c r="K9">
-        <v>45.6</v>
+      <c r="I9" s="73">
+        <v>25</v>
+      </c>
+      <c r="J9" s="73">
+        <v>29.7</v>
+      </c>
+      <c r="K9" s="73">
+        <v>45.2</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10">
-        <v>2018</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="A10" s="73">
+        <v>2017</v>
+      </c>
+      <c r="B10" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="D10">
-        <v>7144614</v>
-      </c>
-      <c r="E10">
-        <v>1476936</v>
-      </c>
-      <c r="F10">
-        <v>2234894</v>
-      </c>
-      <c r="G10">
-        <v>3432784</v>
-      </c>
-      <c r="H10">
+      <c r="D10" s="73">
+        <v>7209286</v>
+      </c>
+      <c r="E10" s="73">
+        <v>1427089</v>
+      </c>
+      <c r="F10" s="73">
+        <v>2357382</v>
+      </c>
+      <c r="G10" s="73">
+        <v>3424815</v>
+      </c>
+      <c r="H10" s="73">
         <v>0</v>
       </c>
-      <c r="I10">
-        <v>20.7</v>
-      </c>
-      <c r="J10">
-        <v>31.3</v>
-      </c>
-      <c r="K10">
-        <v>48</v>
+      <c r="I10" s="73">
+        <v>19.8</v>
+      </c>
+      <c r="J10" s="73">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="K10" s="73">
+        <v>47.5</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B11" t="s">
         <v>53</v>
@@ -5520,33 +5696,33 @@
         <v>30</v>
       </c>
       <c r="D11">
-        <v>2290979</v>
+        <v>2216890</v>
       </c>
       <c r="E11">
-        <v>307035</v>
+        <v>300013</v>
       </c>
       <c r="F11">
-        <v>680637</v>
+        <v>666935</v>
       </c>
       <c r="G11">
-        <v>1303307</v>
+        <v>1249942</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="J11">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="K11">
-        <v>56.9</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B12" t="s">
         <v>53</v>
@@ -5555,33 +5731,33 @@
         <v>33</v>
       </c>
       <c r="D12">
-        <v>2738143</v>
+        <v>2707923</v>
       </c>
       <c r="E12">
-        <v>516530</v>
+        <v>545494</v>
       </c>
       <c r="F12">
-        <v>847492</v>
+        <v>824714</v>
       </c>
       <c r="G12">
-        <v>1374121</v>
+        <v>1337715</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>18.899999999999999</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="J12">
-        <v>31</v>
+        <v>30.5</v>
       </c>
       <c r="K12">
-        <v>50.2</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B13" t="s">
         <v>54</v>
@@ -5590,33 +5766,33 @@
         <v>30</v>
       </c>
       <c r="D13">
-        <v>836437</v>
+        <v>820183</v>
       </c>
       <c r="E13">
-        <v>158421</v>
+        <v>125502</v>
       </c>
       <c r="F13">
-        <v>412179</v>
+        <v>386785</v>
       </c>
       <c r="G13">
-        <v>265837</v>
+        <v>307896</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>18.899999999999999</v>
+        <v>15.3</v>
       </c>
       <c r="J13">
-        <v>49.3</v>
+        <v>47.2</v>
       </c>
       <c r="K13">
-        <v>31.8</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B14" t="s">
         <v>54</v>
@@ -5625,33 +5801,33 @@
         <v>33</v>
       </c>
       <c r="D14">
-        <v>1352582</v>
+        <v>1399618</v>
       </c>
       <c r="E14">
-        <v>483436</v>
+        <v>505927</v>
       </c>
       <c r="F14">
-        <v>328103</v>
+        <v>356460</v>
       </c>
       <c r="G14">
-        <v>541043</v>
+        <v>537231</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>35.700000000000003</v>
+        <v>36.1</v>
       </c>
       <c r="J14">
-        <v>24.3</v>
+        <v>25.5</v>
       </c>
       <c r="K14">
-        <v>40</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B15" t="s">
         <v>53</v>
@@ -5660,33 +5836,33 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>5029122</v>
+        <v>4924813</v>
       </c>
       <c r="E15">
-        <v>823565</v>
+        <v>845507</v>
       </c>
       <c r="F15">
-        <v>1528129</v>
+        <v>1491649</v>
       </c>
       <c r="G15">
-        <v>2677428</v>
+        <v>2587657</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>16.399999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="J15">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="K15">
-        <v>53.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B16" t="s">
         <v>54</v>
@@ -5695,33 +5871,33 @@
         <v>10</v>
       </c>
       <c r="D16">
-        <v>2189019</v>
+        <v>2219801</v>
       </c>
       <c r="E16">
-        <v>641857</v>
+        <v>631429</v>
       </c>
       <c r="F16">
-        <v>740282</v>
+        <v>743245</v>
       </c>
       <c r="G16">
-        <v>806880</v>
+        <v>845127</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>29.3</v>
+        <v>28.4</v>
       </c>
       <c r="J16">
-        <v>33.799999999999997</v>
+        <v>33.5</v>
       </c>
       <c r="K16">
-        <v>36.9</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B17" t="s">
         <v>10</v>
@@ -5730,33 +5906,33 @@
         <v>30</v>
       </c>
       <c r="D17">
-        <v>3127416</v>
+        <v>3037073</v>
       </c>
       <c r="E17">
-        <v>465456</v>
+        <v>425515</v>
       </c>
       <c r="F17">
-        <v>1092816</v>
+        <v>1053720</v>
       </c>
       <c r="G17">
-        <v>1569144</v>
+        <v>1557838</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>14.9</v>
+        <v>14</v>
       </c>
       <c r="J17">
-        <v>34.9</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="K17">
-        <v>50.2</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -5765,33 +5941,33 @@
         <v>33</v>
       </c>
       <c r="D18">
-        <v>4090725</v>
+        <v>4107541</v>
       </c>
       <c r="E18">
-        <v>999966</v>
+        <v>1051421</v>
       </c>
       <c r="F18">
-        <v>1175595</v>
+        <v>1181174</v>
       </c>
       <c r="G18">
-        <v>1915164</v>
+        <v>1874946</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
       <c r="J18">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="K18">
-        <v>46.8</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -5800,33 +5976,33 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>7218141</v>
+        <v>7144614</v>
       </c>
       <c r="E19">
-        <v>1465422</v>
+        <v>1476936</v>
       </c>
       <c r="F19">
-        <v>2268411</v>
+        <v>2234894</v>
       </c>
       <c r="G19">
-        <v>3484308</v>
+        <v>3432784</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="J19">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="K19">
-        <v>48.3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B20" t="s">
         <v>53</v>
@@ -5835,33 +6011,33 @@
         <v>30</v>
       </c>
       <c r="D20">
-        <v>1952530</v>
+        <v>2290979</v>
       </c>
       <c r="E20">
-        <v>303597</v>
+        <v>307035</v>
       </c>
       <c r="F20">
-        <v>491701</v>
+        <v>680637</v>
       </c>
       <c r="G20">
-        <v>1157232</v>
+        <v>1303307</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>15.5</v>
+        <v>13.4</v>
       </c>
       <c r="J20">
-        <v>25.2</v>
+        <v>29.7</v>
       </c>
       <c r="K20">
-        <v>59.3</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B21" t="s">
         <v>53</v>
@@ -5870,33 +6046,33 @@
         <v>33</v>
       </c>
       <c r="D21">
-        <v>2441511</v>
+        <v>2738143</v>
       </c>
       <c r="E21">
-        <v>474809</v>
+        <v>516530</v>
       </c>
       <c r="F21">
-        <v>605321</v>
+        <v>847492</v>
       </c>
       <c r="G21">
-        <v>1361381</v>
+        <v>1374121</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>19.399999999999999</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="J21">
-        <v>24.8</v>
+        <v>31</v>
       </c>
       <c r="K21">
-        <v>55.8</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B22" t="s">
         <v>54</v>
@@ -5905,33 +6081,33 @@
         <v>30</v>
       </c>
       <c r="D22">
-        <v>728994</v>
+        <v>836437</v>
       </c>
       <c r="E22">
-        <v>118086</v>
+        <v>158421</v>
       </c>
       <c r="F22">
-        <v>348498</v>
+        <v>412179</v>
       </c>
       <c r="G22">
-        <v>262410</v>
+        <v>265837</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
       <c r="I22">
-        <v>16.2</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="J22">
-        <v>47.8</v>
+        <v>49.3</v>
       </c>
       <c r="K22">
-        <v>36</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B23" t="s">
         <v>54</v>
@@ -5940,33 +6116,33 @@
         <v>33</v>
       </c>
       <c r="D23">
-        <v>1157282</v>
+        <v>1352582</v>
       </c>
       <c r="E23">
-        <v>392695</v>
+        <v>483436</v>
       </c>
       <c r="F23">
-        <v>290242</v>
+        <v>328103</v>
       </c>
       <c r="G23">
-        <v>474345</v>
+        <v>541043</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>33.9</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="J23">
-        <v>25.1</v>
+        <v>24.3</v>
       </c>
       <c r="K23">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B24" t="s">
         <v>53</v>
@@ -5975,33 +6151,33 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>4394041</v>
+        <v>5029122</v>
       </c>
       <c r="E24">
-        <v>778406</v>
+        <v>823565</v>
       </c>
       <c r="F24">
-        <v>1097022</v>
+        <v>1528129</v>
       </c>
       <c r="G24">
-        <v>2518613</v>
+        <v>2677428</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>17.7</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="J24">
-        <v>25</v>
+        <v>30.4</v>
       </c>
       <c r="K24">
-        <v>57.3</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B25" t="s">
         <v>54</v>
@@ -6010,33 +6186,33 @@
         <v>10</v>
       </c>
       <c r="D25">
-        <v>1886276</v>
+        <v>2189019</v>
       </c>
       <c r="E25">
-        <v>510781</v>
+        <v>641857</v>
       </c>
       <c r="F25">
-        <v>638740</v>
+        <v>740282</v>
       </c>
       <c r="G25">
-        <v>736755</v>
+        <v>806880</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>27.1</v>
+        <v>29.3</v>
       </c>
       <c r="J25">
-        <v>33.9</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="K25">
-        <v>39.1</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B26" t="s">
         <v>10</v>
@@ -6045,33 +6221,33 @@
         <v>30</v>
       </c>
       <c r="D26">
-        <v>2681524</v>
+        <v>3127416</v>
       </c>
       <c r="E26">
-        <v>421683</v>
+        <v>465456</v>
       </c>
       <c r="F26">
-        <v>840199</v>
+        <v>1092816</v>
       </c>
       <c r="G26">
-        <v>1419642</v>
+        <v>1569144</v>
       </c>
       <c r="H26">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>15.7</v>
+        <v>14.9</v>
       </c>
       <c r="J26">
-        <v>31.3</v>
+        <v>34.9</v>
       </c>
       <c r="K26">
-        <v>52.9</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B27" t="s">
         <v>10</v>
@@ -6080,33 +6256,33 @@
         <v>33</v>
       </c>
       <c r="D27">
-        <v>3598793</v>
+        <v>4090725</v>
       </c>
       <c r="E27">
-        <v>867504</v>
+        <v>999966</v>
       </c>
       <c r="F27">
-        <v>895563</v>
+        <v>1175595</v>
       </c>
       <c r="G27">
-        <v>1835726</v>
+        <v>1915164</v>
       </c>
       <c r="H27">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="J27">
-        <v>24.9</v>
+        <v>28.7</v>
       </c>
       <c r="K27">
-        <v>51</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B28" t="s">
         <v>10</v>
@@ -6115,33 +6291,33 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>6280317</v>
+        <v>7218141</v>
       </c>
       <c r="E28">
-        <v>1289187</v>
+        <v>1465422</v>
       </c>
       <c r="F28">
-        <v>1735762</v>
+        <v>2268411</v>
       </c>
       <c r="G28">
-        <v>3255368</v>
+        <v>3484308</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="J28">
-        <v>27.6</v>
+        <v>31.4</v>
       </c>
       <c r="K28">
-        <v>51.8</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B29" t="s">
         <v>53</v>
@@ -6150,33 +6326,33 @@
         <v>30</v>
       </c>
       <c r="D29">
-        <v>2181679</v>
+        <v>1952530</v>
       </c>
       <c r="E29">
-        <v>292158</v>
+        <v>303597</v>
       </c>
       <c r="F29">
-        <v>616126</v>
+        <v>491701</v>
       </c>
       <c r="G29">
-        <v>1273395</v>
+        <v>1157232</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
       <c r="I29">
-        <v>13.4</v>
+        <v>15.5</v>
       </c>
       <c r="J29">
-        <v>28.2</v>
+        <v>25.2</v>
       </c>
       <c r="K29">
-        <v>58.4</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
@@ -6185,33 +6361,33 @@
         <v>33</v>
       </c>
       <c r="D30">
-        <v>2616787</v>
+        <v>2441511</v>
       </c>
       <c r="E30">
-        <v>484674</v>
+        <v>474809</v>
       </c>
       <c r="F30">
-        <v>724972</v>
+        <v>605321</v>
       </c>
       <c r="G30">
-        <v>1407141</v>
+        <v>1361381</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>18.5</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="J30">
-        <v>27.7</v>
+        <v>24.8</v>
       </c>
       <c r="K30">
-        <v>53.8</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B31" t="s">
         <v>54</v>
@@ -6220,33 +6396,33 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>735695</v>
+        <v>728994</v>
       </c>
       <c r="E31">
-        <v>135233</v>
+        <v>118086</v>
       </c>
       <c r="F31">
-        <v>327338</v>
+        <v>348498</v>
       </c>
       <c r="G31">
-        <v>273124</v>
+        <v>262410</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>18.399999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="J31">
-        <v>44.5</v>
+        <v>47.8</v>
       </c>
       <c r="K31">
-        <v>37.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B32" t="s">
         <v>54</v>
@@ -6255,33 +6431,33 @@
         <v>33</v>
       </c>
       <c r="D32">
-        <v>1245586</v>
+        <v>1157282</v>
       </c>
       <c r="E32">
-        <v>426891</v>
+        <v>392695</v>
       </c>
       <c r="F32">
-        <v>320096</v>
+        <v>290242</v>
       </c>
       <c r="G32">
-        <v>498599</v>
+        <v>474345</v>
       </c>
       <c r="H32">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>34.299999999999997</v>
+        <v>33.9</v>
       </c>
       <c r="J32">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="K32">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B33" t="s">
         <v>53</v>
@@ -6290,33 +6466,33 @@
         <v>10</v>
       </c>
       <c r="D33">
-        <v>4798466</v>
+        <v>4394041</v>
       </c>
       <c r="E33">
-        <v>776832</v>
+        <v>778406</v>
       </c>
       <c r="F33">
-        <v>1341098</v>
+        <v>1097022</v>
       </c>
       <c r="G33">
-        <v>2680536</v>
+        <v>2518613</v>
       </c>
       <c r="H33">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>16.2</v>
+        <v>17.7</v>
       </c>
       <c r="J33">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="K33">
-        <v>55.9</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B34" t="s">
         <v>54</v>
@@ -6325,33 +6501,33 @@
         <v>10</v>
       </c>
       <c r="D34">
-        <v>1981281</v>
+        <v>1886276</v>
       </c>
       <c r="E34">
-        <v>562124</v>
+        <v>510781</v>
       </c>
       <c r="F34">
-        <v>647434</v>
+        <v>638740</v>
       </c>
       <c r="G34">
-        <v>771723</v>
+        <v>736755</v>
       </c>
       <c r="H34">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>28.4</v>
+        <v>27.1</v>
       </c>
       <c r="J34">
-        <v>32.700000000000003</v>
+        <v>33.9</v>
       </c>
       <c r="K34">
-        <v>39</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
@@ -6360,33 +6536,33 @@
         <v>30</v>
       </c>
       <c r="D35">
-        <v>2917374</v>
+        <v>2681524</v>
       </c>
       <c r="E35">
-        <v>427391</v>
+        <v>421683</v>
       </c>
       <c r="F35">
-        <v>943464</v>
+        <v>840199</v>
       </c>
       <c r="G35">
-        <v>1546519</v>
+        <v>1419642</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="J35">
-        <v>32.299999999999997</v>
+        <v>31.3</v>
       </c>
       <c r="K35">
-        <v>53</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -6395,33 +6571,33 @@
         <v>33</v>
       </c>
       <c r="D36">
-        <v>3862373</v>
+        <v>3598793</v>
       </c>
       <c r="E36">
-        <v>911565</v>
+        <v>867504</v>
       </c>
       <c r="F36">
-        <v>1045068</v>
+        <v>895563</v>
       </c>
       <c r="G36">
-        <v>1905740</v>
+        <v>1835726</v>
       </c>
       <c r="H36">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="J36">
-        <v>27.1</v>
+        <v>24.9</v>
       </c>
       <c r="K36">
-        <v>49.3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B37" t="s">
         <v>10</v>
@@ -6430,33 +6606,33 @@
         <v>10</v>
       </c>
       <c r="D37">
-        <v>6779747</v>
+        <v>6280317</v>
       </c>
       <c r="E37">
-        <v>1338956</v>
+        <v>1289187</v>
       </c>
       <c r="F37">
-        <v>1988532</v>
+        <v>1735762</v>
       </c>
       <c r="G37">
-        <v>3452259</v>
+        <v>3255368</v>
       </c>
       <c r="H37">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>19.7</v>
+        <v>20.5</v>
       </c>
       <c r="J37">
-        <v>29.3</v>
+        <v>27.6</v>
       </c>
       <c r="K37">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
@@ -6465,33 +6641,33 @@
         <v>30</v>
       </c>
       <c r="D38">
-        <v>2165742</v>
+        <v>2181679</v>
       </c>
       <c r="E38">
-        <v>312784</v>
+        <v>292158</v>
       </c>
       <c r="F38">
-        <v>608194</v>
+        <v>616126</v>
       </c>
       <c r="G38">
-        <v>1244764</v>
+        <v>1273395</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>14.4</v>
+        <v>13.4</v>
       </c>
       <c r="J38">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="K38">
-        <v>57.5</v>
+        <v>58.4</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
@@ -6500,33 +6676,33 @@
         <v>33</v>
       </c>
       <c r="D39">
-        <v>2600732</v>
+        <v>2616787</v>
       </c>
       <c r="E39">
-        <v>574232</v>
+        <v>484674</v>
       </c>
       <c r="F39">
-        <v>718995</v>
+        <v>724972</v>
       </c>
       <c r="G39">
-        <v>1307505</v>
+        <v>1407141</v>
       </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>22.1</v>
+        <v>18.5</v>
       </c>
       <c r="J39">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="K39">
-        <v>50.3</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -6535,33 +6711,33 @@
         <v>30</v>
       </c>
       <c r="D40">
-        <v>813892</v>
+        <v>735695</v>
       </c>
       <c r="E40">
-        <v>163960</v>
+        <v>135233</v>
       </c>
       <c r="F40">
-        <v>368413</v>
+        <v>327338</v>
       </c>
       <c r="G40">
-        <v>281519</v>
+        <v>273124</v>
       </c>
       <c r="H40">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>20.100000000000001</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="J40">
-        <v>45.3</v>
+        <v>44.5</v>
       </c>
       <c r="K40">
-        <v>34.6</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -6570,33 +6746,33 @@
         <v>33</v>
       </c>
       <c r="D41">
-        <v>1346556</v>
+        <v>1245586</v>
       </c>
       <c r="E41">
-        <v>485899</v>
+        <v>426891</v>
       </c>
       <c r="F41">
-        <v>330447</v>
+        <v>320096</v>
       </c>
       <c r="G41">
-        <v>530210</v>
+        <v>498599</v>
       </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>36.1</v>
+        <v>34.299999999999997</v>
       </c>
       <c r="J41">
-        <v>24.5</v>
+        <v>25.7</v>
       </c>
       <c r="K41">
-        <v>39.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B42" t="s">
         <v>53</v>
@@ -6605,33 +6781,33 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>4766474</v>
+        <v>4798466</v>
       </c>
       <c r="E42">
-        <v>887016</v>
+        <v>776832</v>
       </c>
       <c r="F42">
-        <v>1327189</v>
+        <v>1341098</v>
       </c>
       <c r="G42">
-        <v>2552269</v>
+        <v>2680536</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42">
-        <v>18.600000000000001</v>
+        <v>16.2</v>
       </c>
       <c r="J42">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="K42">
-        <v>53.5</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
@@ -6640,33 +6816,33 @@
         <v>10</v>
       </c>
       <c r="D43">
-        <v>2160448</v>
+        <v>1981281</v>
       </c>
       <c r="E43">
-        <v>649859</v>
+        <v>562124</v>
       </c>
       <c r="F43">
-        <v>698860</v>
+        <v>647434</v>
       </c>
       <c r="G43">
-        <v>811729</v>
+        <v>771723</v>
       </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>30.1</v>
+        <v>28.4</v>
       </c>
       <c r="J43">
-        <v>32.299999999999997</v>
+        <v>32.700000000000003</v>
       </c>
       <c r="K43">
-        <v>37.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B44" t="s">
         <v>10</v>
@@ -6675,33 +6851,33 @@
         <v>30</v>
       </c>
       <c r="D44">
-        <v>2979634</v>
+        <v>2917374</v>
       </c>
       <c r="E44">
-        <v>476744</v>
+        <v>427391</v>
       </c>
       <c r="F44">
-        <v>976607</v>
+        <v>943464</v>
       </c>
       <c r="G44">
-        <v>1526283</v>
+        <v>1546519</v>
       </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="J44">
-        <v>32.799999999999997</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="K44">
-        <v>51.2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
@@ -6710,33 +6886,33 @@
         <v>33</v>
       </c>
       <c r="D45">
-        <v>3947288</v>
+        <v>3862373</v>
       </c>
       <c r="E45">
-        <v>1060131</v>
+        <v>911565</v>
       </c>
       <c r="F45">
-        <v>1049442</v>
+        <v>1045068</v>
       </c>
       <c r="G45">
-        <v>1837715</v>
+        <v>1905740</v>
       </c>
       <c r="H45">
         <v>0</v>
       </c>
       <c r="I45">
-        <v>26.9</v>
+        <v>23.6</v>
       </c>
       <c r="J45">
-        <v>26.6</v>
+        <v>27.1</v>
       </c>
       <c r="K45">
-        <v>46.6</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
@@ -6745,33 +6921,33 @@
         <v>10</v>
       </c>
       <c r="D46">
-        <v>6926922</v>
+        <v>6779747</v>
       </c>
       <c r="E46">
-        <v>1536875</v>
+        <v>1338956</v>
       </c>
       <c r="F46">
-        <v>2026049</v>
+        <v>1988532</v>
       </c>
       <c r="G46">
-        <v>3363998</v>
+        <v>3452259</v>
       </c>
       <c r="H46">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>22.2</v>
+        <v>19.7</v>
       </c>
       <c r="J46">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="K46">
-        <v>48.6</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -6780,33 +6956,33 @@
         <v>30</v>
       </c>
       <c r="D47">
-        <v>2191369</v>
+        <v>2165742</v>
       </c>
       <c r="E47">
-        <v>400545</v>
+        <v>312784</v>
       </c>
       <c r="F47">
-        <v>591635</v>
+        <v>608194</v>
       </c>
       <c r="G47">
-        <v>1199189</v>
+        <v>1244764</v>
       </c>
       <c r="H47">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>18.3</v>
+        <v>14.4</v>
       </c>
       <c r="J47">
-        <v>27</v>
+        <v>28.1</v>
       </c>
       <c r="K47">
-        <v>54.7</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -6815,33 +6991,33 @@
         <v>33</v>
       </c>
       <c r="D48">
-        <v>2673806</v>
+        <v>2600732</v>
       </c>
       <c r="E48">
-        <v>587899</v>
+        <v>574232</v>
       </c>
       <c r="F48">
-        <v>727381</v>
+        <v>718995</v>
       </c>
       <c r="G48">
-        <v>1358526</v>
+        <v>1307505</v>
       </c>
       <c r="H48">
         <v>0</v>
       </c>
       <c r="I48">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="J48">
-        <v>27.2</v>
+        <v>27.6</v>
       </c>
       <c r="K48">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -6850,33 +7026,33 @@
         <v>30</v>
       </c>
       <c r="D49">
-        <v>784750</v>
+        <v>813892</v>
       </c>
       <c r="E49">
-        <v>165404</v>
+        <v>163960</v>
       </c>
       <c r="F49">
-        <v>360272</v>
+        <v>368413</v>
       </c>
       <c r="G49">
-        <v>259074</v>
+        <v>281519</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49">
-        <v>21.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="J49">
-        <v>45.9</v>
+        <v>45.3</v>
       </c>
       <c r="K49">
-        <v>33</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -6885,33 +7061,33 @@
         <v>33</v>
       </c>
       <c r="D50">
-        <v>1317482</v>
+        <v>1346556</v>
       </c>
       <c r="E50">
-        <v>463609</v>
+        <v>485899</v>
       </c>
       <c r="F50">
-        <v>336112</v>
+        <v>330447</v>
       </c>
       <c r="G50">
-        <v>517761</v>
+        <v>530210</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>35.200000000000003</v>
+        <v>36.1</v>
       </c>
       <c r="J50">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="K50">
-        <v>39.299999999999997</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B51" t="s">
         <v>53</v>
@@ -6920,33 +7096,33 @@
         <v>10</v>
       </c>
       <c r="D51">
-        <v>4865175</v>
+        <v>4766474</v>
       </c>
       <c r="E51">
-        <v>988444</v>
+        <v>887016</v>
       </c>
       <c r="F51">
-        <v>1319016</v>
+        <v>1327189</v>
       </c>
       <c r="G51">
-        <v>2557715</v>
+        <v>2552269</v>
       </c>
       <c r="H51">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>20.3</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="J51">
-        <v>27.1</v>
+        <v>27.8</v>
       </c>
       <c r="K51">
-        <v>52.6</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B52" t="s">
         <v>54</v>
@@ -6955,33 +7131,33 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>2102232</v>
+        <v>2160448</v>
       </c>
       <c r="E52">
-        <v>629013</v>
+        <v>649859</v>
       </c>
       <c r="F52">
-        <v>696384</v>
+        <v>698860</v>
       </c>
       <c r="G52">
-        <v>776835</v>
+        <v>811729</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="J52">
-        <v>33.1</v>
+        <v>32.299999999999997</v>
       </c>
       <c r="K52">
-        <v>37</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B53" t="s">
         <v>10</v>
@@ -6990,33 +7166,33 @@
         <v>30</v>
       </c>
       <c r="D53">
-        <v>2976119</v>
+        <v>2979634</v>
       </c>
       <c r="E53">
-        <v>565949</v>
+        <v>476744</v>
       </c>
       <c r="F53">
-        <v>951907</v>
+        <v>976607</v>
       </c>
       <c r="G53">
-        <v>1458263</v>
+        <v>1526283</v>
       </c>
       <c r="H53">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J53">
-        <v>32</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="K53">
-        <v>49</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B54" t="s">
         <v>10</v>
@@ -7025,33 +7201,33 @@
         <v>33</v>
       </c>
       <c r="D54">
-        <v>3991288</v>
+        <v>3947288</v>
       </c>
       <c r="E54">
-        <v>1051508</v>
+        <v>1060131</v>
       </c>
       <c r="F54">
-        <v>1063493</v>
+        <v>1049442</v>
       </c>
       <c r="G54">
-        <v>1876287</v>
+        <v>1837715</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="J54">
         <v>26.6</v>
       </c>
       <c r="K54">
-        <v>47</v>
+        <v>46.6</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B55" t="s">
         <v>10</v>
@@ -7060,27 +7236,342 @@
         <v>10</v>
       </c>
       <c r="D55">
-        <v>6967407</v>
+        <v>6926922</v>
       </c>
       <c r="E55">
-        <v>1617457</v>
+        <v>1536875</v>
       </c>
       <c r="F55">
-        <v>2015400</v>
+        <v>2026049</v>
       </c>
       <c r="G55">
-        <v>3334550</v>
+        <v>3363998</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55">
+        <v>22.2</v>
+      </c>
+      <c r="J55">
+        <v>29.2</v>
+      </c>
+      <c r="K55">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
+      <c r="A56">
+        <v>2023</v>
+      </c>
+      <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56">
+        <v>2191369</v>
+      </c>
+      <c r="E56">
+        <v>400545</v>
+      </c>
+      <c r="F56">
+        <v>591635</v>
+      </c>
+      <c r="G56">
+        <v>1199189</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>18.3</v>
+      </c>
+      <c r="J56">
+        <v>27</v>
+      </c>
+      <c r="K56">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57">
+        <v>2023</v>
+      </c>
+      <c r="B57" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57">
+        <v>2673806</v>
+      </c>
+      <c r="E57">
+        <v>587899</v>
+      </c>
+      <c r="F57">
+        <v>727381</v>
+      </c>
+      <c r="G57">
+        <v>1358526</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>22</v>
+      </c>
+      <c r="J57">
+        <v>27.2</v>
+      </c>
+      <c r="K57">
+        <v>50.8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
+      <c r="A58">
+        <v>2023</v>
+      </c>
+      <c r="B58" t="s">
+        <v>54</v>
+      </c>
+      <c r="C58" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58">
+        <v>784750</v>
+      </c>
+      <c r="E58">
+        <v>165404</v>
+      </c>
+      <c r="F58">
+        <v>360272</v>
+      </c>
+      <c r="G58">
+        <v>259074</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>21.1</v>
+      </c>
+      <c r="J58">
+        <v>45.9</v>
+      </c>
+      <c r="K58">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59">
+        <v>2023</v>
+      </c>
+      <c r="B59" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59">
+        <v>1317482</v>
+      </c>
+      <c r="E59">
+        <v>463609</v>
+      </c>
+      <c r="F59">
+        <v>336112</v>
+      </c>
+      <c r="G59">
+        <v>517761</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="J59">
+        <v>25.5</v>
+      </c>
+      <c r="K59">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60">
+        <v>2023</v>
+      </c>
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" t="s">
+        <v>10</v>
+      </c>
+      <c r="D60">
+        <v>4865175</v>
+      </c>
+      <c r="E60">
+        <v>988444</v>
+      </c>
+      <c r="F60">
+        <v>1319016</v>
+      </c>
+      <c r="G60">
+        <v>2557715</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>20.3</v>
+      </c>
+      <c r="J60">
+        <v>27.1</v>
+      </c>
+      <c r="K60">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61">
+        <v>2023</v>
+      </c>
+      <c r="B61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" t="s">
+        <v>10</v>
+      </c>
+      <c r="D61">
+        <v>2102232</v>
+      </c>
+      <c r="E61">
+        <v>629013</v>
+      </c>
+      <c r="F61">
+        <v>696384</v>
+      </c>
+      <c r="G61">
+        <v>776835</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>29.9</v>
+      </c>
+      <c r="J61">
+        <v>33.1</v>
+      </c>
+      <c r="K61">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62">
+        <v>2023</v>
+      </c>
+      <c r="B62" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>2976119</v>
+      </c>
+      <c r="E62">
+        <v>565949</v>
+      </c>
+      <c r="F62">
+        <v>951907</v>
+      </c>
+      <c r="G62">
+        <v>1458263</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>19</v>
+      </c>
+      <c r="J62">
+        <v>32</v>
+      </c>
+      <c r="K62">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63">
+        <v>2023</v>
+      </c>
+      <c r="B63" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63">
+        <v>3991288</v>
+      </c>
+      <c r="E63">
+        <v>1051508</v>
+      </c>
+      <c r="F63">
+        <v>1063493</v>
+      </c>
+      <c r="G63">
+        <v>1876287</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>26.3</v>
+      </c>
+      <c r="J63">
+        <v>26.6</v>
+      </c>
+      <c r="K63">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
+      <c r="A64">
+        <v>2023</v>
+      </c>
+      <c r="B64" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64">
+        <v>6967407</v>
+      </c>
+      <c r="E64">
+        <v>1617457</v>
+      </c>
+      <c r="F64">
+        <v>2015400</v>
+      </c>
+      <c r="G64">
+        <v>3334550</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
         <v>23.2</v>
       </c>
-      <c r="J55">
+      <c r="J64">
         <v>28.9</v>
       </c>
-      <c r="K55">
+      <c r="K64">
         <v>47.9</v>
       </c>
     </row>
@@ -8149,64 +8640,88 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A775D371-C279-4270-BB7B-D597EDE2A98B}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" style="71"/>
+    <col min="2" max="2" width="19.33203125" style="71" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="71" customWidth="1"/>
+    <col min="4" max="16384" width="11.5546875" style="71"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="71" t="s">
         <v>80</v>
       </c>
-      <c r="B1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1970</v>
-      </c>
-      <c r="B2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1980</v>
-      </c>
-      <c r="B3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>1991</v>
-      </c>
-      <c r="B4">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
+      <c r="B1" s="71" t="s">
+        <v>207</v>
+      </c>
+      <c r="C1" s="71" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1" s="71" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="71" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="71">
         <v>2001</v>
       </c>
-      <c r="B5">
+      <c r="B2" s="71">
         <v>35</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
+      <c r="C2" s="72">
+        <v>8.9</v>
+      </c>
+      <c r="D2" s="72">
+        <v>10.6</v>
+      </c>
+      <c r="E2" s="72">
+        <v>6.4</v>
+      </c>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="71">
         <v>2010</v>
       </c>
-      <c r="B6">
+      <c r="B3" s="71">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
+      <c r="C3" s="72">
+        <v>10.4</v>
+      </c>
+      <c r="D3" s="72">
+        <v>12.5</v>
+      </c>
+      <c r="E3" s="72">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="71">
         <v>2022</v>
       </c>
-      <c r="B7">
+      <c r="B4" s="71">
         <v>53</v>
       </c>
+      <c r="C4" s="72">
+        <v>10.4</v>
+      </c>
+      <c r="D4" s="72">
+        <v>12.3</v>
+      </c>
+      <c r="E4" s="72">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="C8" s="72"/>
+      <c r="D8" s="72"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9470,25 +9985,25 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="15">
+      <c r="A6" s="19">
         <v>2017</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="20">
         <v>2004772.6666666665</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="21">
         <v>926038.66666666663</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="22">
         <v>1078734</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="20">
         <v>3240408.9166666665</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="21">
         <v>2484153.5</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="22">
         <v>756255.41666666663</v>
       </c>
     </row>
